--- a/results/logs/SK_benchmark_summary.xlsx
+++ b/results/logs/SK_benchmark_summary.xlsx
@@ -478,20 +478,20 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>bur26a</t>
+          <t>nug12</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="C2" t="n">
-        <v>5666705</v>
+        <v>744</v>
       </c>
       <c r="D2" t="n">
-        <v>5426670</v>
+        <v>578</v>
       </c>
       <c r="E2" t="n">
-        <v>4.423246668767403</v>
+        <v>28.719723183391</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -505,7 +505,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>12.26922082901001</v>
+        <v>658.2745223045349</v>
       </c>
     </row>
   </sheetData>
